--- a/output/yearly_benthic_cover_iteration_45_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_45_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.30180417875236</v>
+        <v>45.52347777819554</v>
       </c>
       <c r="M2" t="n">
-        <v>99.71354367270314</v>
+        <v>100.587058713254</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.06671094395311</v>
+        <v>87.98444048633721</v>
       </c>
       <c r="C3" t="n">
-        <v>45.94892473392643</v>
+        <v>45.92503928952057</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228816304183189</v>
+        <v>2.228623364505739</v>
       </c>
       <c r="E3" t="n">
-        <v>5.720051983136814</v>
+        <v>5.701855414797826</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429387680610631</v>
+        <v>0.7428744548352464</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97973986406119</v>
+        <v>33.97231992272351</v>
       </c>
       <c r="H3" t="n">
-        <v>34.1751833308089</v>
+        <v>34.17222492242133</v>
       </c>
       <c r="I3" t="n">
-        <v>6.576613393320295</v>
+        <v>6.523577064333261</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643367300381644</v>
+        <v>4.64296534272029</v>
       </c>
       <c r="K3" t="n">
-        <v>11.93328905604691</v>
+        <v>12.01555951366279</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88172859034838</v>
+        <v>48.82522696466126</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7639423803217</v>
+        <v>106.7658257678446</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.16806170968991</v>
+        <v>87.01052204325595</v>
       </c>
       <c r="C4" t="n">
-        <v>42.68631621202914</v>
+        <v>42.57780708382734</v>
       </c>
       <c r="D4" t="n">
-        <v>2.185626995331294</v>
+        <v>2.181367953261001</v>
       </c>
       <c r="E4" t="n">
-        <v>6.524547452677078</v>
+        <v>6.488897364999045</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444990625625789</v>
+        <v>0.7444248141512098</v>
       </c>
       <c r="G4" t="n">
-        <v>33.3212910376857</v>
+        <v>33.25197570734186</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24695687787862</v>
+        <v>34.24354145095564</v>
       </c>
       <c r="I4" t="n">
-        <v>5.492021142538525</v>
+        <v>5.447659664102113</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653119141016117</v>
+        <v>4.65265508844506</v>
       </c>
       <c r="K4" t="n">
-        <v>12.83193829031008</v>
+        <v>12.98947795674407</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29906179229079</v>
+        <v>44.25150448541933</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81731629463</v>
+        <v>99.81878952599074</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.1181481218664</v>
+        <v>85.73112248793335</v>
       </c>
       <c r="C5" t="n">
-        <v>42.48883167467459</v>
+        <v>42.14388568222246</v>
       </c>
       <c r="D5" t="n">
-        <v>2.134813487454837</v>
+        <v>2.118535526086275</v>
       </c>
       <c r="E5" t="n">
-        <v>7.136993008502777</v>
+        <v>7.059947526121908</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458202644844647</v>
+        <v>0.7457411207182818</v>
       </c>
       <c r="G5" t="n">
-        <v>32.54660638737075</v>
+        <v>32.29418115510965</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30773216628537</v>
+        <v>34.30409155304095</v>
       </c>
       <c r="I5" t="n">
-        <v>4.5848061547403</v>
+        <v>4.547743602366999</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661376653027903</v>
+        <v>4.66088200448926</v>
       </c>
       <c r="K5" t="n">
-        <v>13.8818518781336</v>
+        <v>14.26887751206668</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47676030434351</v>
+        <v>43.43591292615246</v>
       </c>
       <c r="M5" t="n">
-        <v>99.8474438571517</v>
+        <v>99.8486761204416</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.84988100842472</v>
+        <v>84.22148973289676</v>
       </c>
       <c r="C6" t="n">
-        <v>41.93274466697395</v>
+        <v>41.34040362888382</v>
       </c>
       <c r="D6" t="n">
-        <v>2.073180699271432</v>
+        <v>2.04448599674306</v>
       </c>
       <c r="E6" t="n">
-        <v>7.568681448374962</v>
+        <v>7.445759870681665</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469413887819421</v>
+        <v>0.7468613593426445</v>
       </c>
       <c r="G6" t="n">
-        <v>31.60697484140698</v>
+        <v>31.16539719769444</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35930388396932</v>
+        <v>34.35562252976164</v>
       </c>
       <c r="I6" t="n">
-        <v>3.826415066732932</v>
+        <v>3.795479282781764</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668383679887137</v>
+        <v>4.667883495891528</v>
       </c>
       <c r="K6" t="n">
-        <v>15.1501189915753</v>
+        <v>15.77851026710328</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78978061493019</v>
+        <v>42.75475989283605</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87264427347944</v>
+        <v>99.87367378882314</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.36247427501401</v>
+        <v>82.53326626780739</v>
       </c>
       <c r="C7" t="n">
-        <v>41.03981818147086</v>
+        <v>40.24143085975881</v>
       </c>
       <c r="D7" t="n">
-        <v>2.000974420589213</v>
+        <v>1.962095249675992</v>
       </c>
       <c r="E7" t="n">
-        <v>7.8371987941967</v>
+        <v>7.673527327885341</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478949741872765</v>
+        <v>0.7478166383088558</v>
       </c>
       <c r="G7" t="n">
-        <v>30.50614362370245</v>
+        <v>29.90946276632614</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40316881261471</v>
+        <v>34.39956536220736</v>
       </c>
       <c r="I7" t="n">
-        <v>3.19275006105318</v>
+        <v>3.166944933973351</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674343588670477</v>
+        <v>4.673853989430349</v>
       </c>
       <c r="K7" t="n">
-        <v>16.637525724986</v>
+        <v>17.46673373219263</v>
       </c>
       <c r="L7" t="n">
-        <v>42.2163667861339</v>
+        <v>42.18640542797131</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89371069259076</v>
+        <v>99.89457001992274</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.13663144579955</v>
+        <v>87.53541284054218</v>
       </c>
       <c r="C8" t="n">
-        <v>43.32580690028464</v>
+        <v>42.55841072589283</v>
       </c>
       <c r="D8" t="n">
-        <v>2.005182086617188</v>
+        <v>1.966373203822345</v>
       </c>
       <c r="E8" t="n">
-        <v>9.654764292907142</v>
+        <v>9.52197900741435</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494676540991239</v>
+        <v>0.7494471021148783</v>
       </c>
       <c r="G8" t="n">
-        <v>31.00749874185536</v>
+        <v>30.41340146932219</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47551208855969</v>
+        <v>34.47456669728439</v>
       </c>
       <c r="I8" t="n">
-        <v>5.560033743641525</v>
+        <v>5.725600972366045</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684172838119523</v>
+        <v>4.684044388217989</v>
       </c>
       <c r="K8" t="n">
-        <v>11.86336855420045</v>
+        <v>12.4645871594578</v>
       </c>
       <c r="L8" t="n">
-        <v>44.62587899247524</v>
+        <v>44.78656396100385</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81505444696033</v>
+        <v>99.80956184635448</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.95191053246131</v>
+        <v>85.52818443413</v>
       </c>
       <c r="C9" t="n">
-        <v>42.0044187709797</v>
+        <v>41.43919473353464</v>
       </c>
       <c r="D9" t="n">
-        <v>1.905934559638036</v>
+        <v>1.875665525556079</v>
       </c>
       <c r="E9" t="n">
-        <v>9.950513735424339</v>
+        <v>9.879439400756118</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508167827447856</v>
+        <v>0.7508433375494998</v>
       </c>
       <c r="G9" t="n">
-        <v>29.47276651555166</v>
+        <v>29.01044854558447</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53757200626013</v>
+        <v>34.53879352727699</v>
       </c>
       <c r="I9" t="n">
-        <v>4.64170204068746</v>
+        <v>4.780223237722486</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692604892154909</v>
+        <v>4.692770859684374</v>
       </c>
       <c r="K9" t="n">
-        <v>14.04808946753867</v>
+        <v>14.47181556586998</v>
       </c>
       <c r="L9" t="n">
-        <v>43.79304637971381</v>
+        <v>43.92994522914076</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84555461823219</v>
+        <v>99.84095552854539</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.58631625829238</v>
+        <v>83.40286518936475</v>
       </c>
       <c r="C10" t="n">
-        <v>40.35911815817427</v>
+        <v>40.05499745880901</v>
       </c>
       <c r="D10" t="n">
-        <v>1.799619019405537</v>
+        <v>1.780712411481671</v>
       </c>
       <c r="E10" t="n">
-        <v>10.04113780096657</v>
+        <v>10.04428429508366</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519767453338306</v>
+        <v>0.7520406459270725</v>
       </c>
       <c r="G10" t="n">
-        <v>27.82873677780333</v>
+        <v>27.54183253032665</v>
       </c>
       <c r="H10" t="n">
-        <v>34.5909302853562</v>
+        <v>34.59386971264533</v>
       </c>
       <c r="I10" t="n">
-        <v>3.874060971090484</v>
+        <v>3.989871556856141</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699854658336441</v>
+        <v>4.700254037044203</v>
       </c>
       <c r="K10" t="n">
-        <v>16.4136837417076</v>
+        <v>16.59713481063527</v>
       </c>
       <c r="L10" t="n">
-        <v>43.09826193232126</v>
+        <v>43.2150837517301</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87106383220312</v>
+        <v>99.86721602117437</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.17787347145011</v>
+        <v>81.23513900428389</v>
       </c>
       <c r="C11" t="n">
-        <v>38.55109158042951</v>
+        <v>38.50529252507935</v>
       </c>
       <c r="D11" t="n">
-        <v>1.692603042785392</v>
+        <v>1.684956656651296</v>
       </c>
       <c r="E11" t="n">
-        <v>9.982810688679439</v>
+        <v>10.05907038908509</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529749205710702</v>
+        <v>0.7530680628529327</v>
       </c>
       <c r="G11" t="n">
-        <v>26.17387571428483</v>
+        <v>26.06080227167933</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63684634626922</v>
+        <v>34.64113089123489</v>
       </c>
       <c r="I11" t="n">
-        <v>3.232669505290955</v>
+        <v>3.329435339949517</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706093253569188</v>
+        <v>4.706675392830829</v>
       </c>
       <c r="K11" t="n">
-        <v>18.82212652854991</v>
+        <v>18.76486099571611</v>
       </c>
       <c r="L11" t="n">
-        <v>42.51916908626804</v>
+        <v>42.61901671373631</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89238719524747</v>
+        <v>99.88917023453178</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.74486905327842</v>
+        <v>79.01312455631299</v>
       </c>
       <c r="C12" t="n">
-        <v>36.61824182388391</v>
+        <v>36.79830450729073</v>
       </c>
       <c r="D12" t="n">
-        <v>1.585608331327101</v>
+        <v>1.58778022801215</v>
       </c>
       <c r="E12" t="n">
-        <v>9.801260579485406</v>
+        <v>9.941897550479187</v>
       </c>
       <c r="F12" t="n">
-        <v>0.753834552583878</v>
+        <v>0.7539505567572816</v>
       </c>
       <c r="G12" t="n">
-        <v>24.5193434884733</v>
+        <v>24.55779880732561</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67638941885838</v>
+        <v>34.68172561083495</v>
       </c>
       <c r="I12" t="n">
-        <v>2.696966728901105</v>
+        <v>2.777780823170796</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711465953649237</v>
+        <v>4.712190979733009</v>
       </c>
       <c r="K12" t="n">
-        <v>21.25513094672158</v>
+        <v>20.98687544368702</v>
       </c>
       <c r="L12" t="n">
-        <v>42.03683085424754</v>
+        <v>42.12233573402366</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91020362485304</v>
+        <v>99.90751568500141</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.27483156060579</v>
+        <v>76.75873957048459</v>
       </c>
       <c r="C13" t="n">
-        <v>34.56458817154441</v>
+        <v>34.97284504885288</v>
       </c>
       <c r="D13" t="n">
-        <v>1.477983812759572</v>
+        <v>1.490089473158814</v>
       </c>
       <c r="E13" t="n">
-        <v>9.510938632149992</v>
+        <v>9.716397276965665</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545756829985201</v>
+        <v>0.7547092169443205</v>
       </c>
       <c r="G13" t="n">
-        <v>22.855072125614</v>
+        <v>23.04684038833362</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71048141793192</v>
+        <v>34.71662397943873</v>
       </c>
       <c r="I13" t="n">
-        <v>2.249681870411033</v>
+        <v>2.31714662974144</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716098018740751</v>
+        <v>4.716932605902001</v>
       </c>
       <c r="K13" t="n">
-        <v>23.72516843939423</v>
+        <v>23.24126042951542</v>
       </c>
       <c r="L13" t="n">
-        <v>41.63532764659188</v>
+        <v>41.70873394321028</v>
       </c>
       <c r="M13" t="n">
-        <v>99.9250842575305</v>
+        <v>99.92283942157857</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.28377202231252</v>
+        <v>83.53225236625738</v>
       </c>
       <c r="C14" t="n">
-        <v>38.86634895232887</v>
+        <v>39.23010631197538</v>
       </c>
       <c r="D14" t="n">
-        <v>1.479764922885454</v>
+        <v>1.491817461218846</v>
       </c>
       <c r="E14" t="n">
-        <v>11.90977313306869</v>
+        <v>12.08331923746199</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554850179845535</v>
+        <v>0.7555844184266258</v>
       </c>
       <c r="G14" t="n">
-        <v>24.7681635007494</v>
+        <v>24.94487854041662</v>
       </c>
       <c r="H14" t="n">
-        <v>36.63785968129623</v>
+        <v>36.62819504150589</v>
       </c>
       <c r="I14" t="n">
-        <v>3.010944403924744</v>
+        <v>2.906055052061006</v>
       </c>
       <c r="J14" t="n">
-        <v>4.72178136240346</v>
+        <v>4.72240261516641</v>
       </c>
       <c r="K14" t="n">
-        <v>16.71622797768748</v>
+        <v>16.46774763374261</v>
       </c>
       <c r="L14" t="n">
-        <v>44.317179060022</v>
+        <v>44.20538975636431</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89975599003836</v>
+        <v>99.90324370208231</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.46105762867666</v>
+        <v>83.05089164938815</v>
       </c>
       <c r="C15" t="n">
-        <v>38.50865890381954</v>
+        <v>39.17652104777989</v>
       </c>
       <c r="D15" t="n">
-        <v>1.449329863322637</v>
+        <v>1.472127020463057</v>
       </c>
       <c r="E15" t="n">
-        <v>12.08343022379032</v>
+        <v>12.34920083302163</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562520577939601</v>
+        <v>0.75631954540461</v>
       </c>
       <c r="G15" t="n">
-        <v>24.25874438981587</v>
+        <v>24.63698946602954</v>
       </c>
       <c r="H15" t="n">
-        <v>36.67505789997431</v>
+        <v>36.68518893760541</v>
       </c>
       <c r="I15" t="n">
-        <v>2.511667832767281</v>
+        <v>2.42406868808508</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726575361212252</v>
+        <v>4.726997158778811</v>
       </c>
       <c r="K15" t="n">
-        <v>17.53894237132335</v>
+        <v>16.94910835061187</v>
       </c>
       <c r="L15" t="n">
-        <v>43.86876138030364</v>
+        <v>43.79364685016211</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91636265544655</v>
+        <v>99.91927624855386</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.93512877789708</v>
+        <v>80.7694866993053</v>
       </c>
       <c r="C16" t="n">
-        <v>36.37067043849422</v>
+        <v>37.2699081215145</v>
       </c>
       <c r="D16" t="n">
-        <v>1.353640253410009</v>
+        <v>1.385953672500299</v>
       </c>
       <c r="E16" t="n">
-        <v>11.6347892008585</v>
+        <v>11.96327740797991</v>
       </c>
       <c r="F16" t="n">
-        <v>0.756912702284202</v>
+        <v>0.7569505937496251</v>
       </c>
       <c r="G16" t="n">
-        <v>22.65710086726405</v>
+        <v>23.19482324225955</v>
       </c>
       <c r="H16" t="n">
-        <v>36.70709639121704</v>
+        <v>36.71579786197647</v>
       </c>
       <c r="I16" t="n">
-        <v>2.094884973587011</v>
+        <v>2.02174270990429</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730704389276264</v>
+        <v>4.730941210935156</v>
       </c>
       <c r="K16" t="n">
-        <v>20.06487122210293</v>
+        <v>19.23051330069469</v>
       </c>
       <c r="L16" t="n">
-        <v>43.49468978849264</v>
+        <v>43.43224333645512</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93023144908979</v>
+        <v>99.93266475866432</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.64718878185604</v>
+        <v>82.77059286234862</v>
       </c>
       <c r="C17" t="n">
-        <v>37.60347284700038</v>
+        <v>38.71979700271107</v>
       </c>
       <c r="D17" t="n">
-        <v>1.354807849606003</v>
+        <v>1.387067731520693</v>
       </c>
       <c r="E17" t="n">
-        <v>12.42192183565301</v>
+        <v>12.84919191994658</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575655850495163</v>
+        <v>0.7575590467258622</v>
       </c>
       <c r="G17" t="n">
-        <v>23.10161283542603</v>
+        <v>23.75710210033781</v>
       </c>
       <c r="H17" t="n">
-        <v>37.16372732620657</v>
+        <v>37.2889451668423</v>
       </c>
       <c r="I17" t="n">
-        <v>2.112768443355441</v>
+        <v>1.995982854938743</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734784906559478</v>
+        <v>4.734744042036637</v>
       </c>
       <c r="K17" t="n">
-        <v>18.35281121814396</v>
+        <v>17.22940713765138</v>
       </c>
       <c r="L17" t="n">
-        <v>43.97335101405669</v>
+        <v>43.98431653530017</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92963507920103</v>
+        <v>99.93352067566262</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.18216755864795</v>
+        <v>80.47140846134189</v>
       </c>
       <c r="C18" t="n">
-        <v>35.46432694410359</v>
+        <v>36.72895623848792</v>
       </c>
       <c r="D18" t="n">
-        <v>1.265187546217621</v>
+        <v>1.304027200688455</v>
       </c>
       <c r="E18" t="n">
-        <v>11.89387158275978</v>
+        <v>12.35735154940495</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581274918139819</v>
+        <v>0.7580813569406999</v>
       </c>
       <c r="G18" t="n">
-        <v>21.57344516820007</v>
+        <v>22.334819449955</v>
       </c>
       <c r="H18" t="n">
-        <v>37.19129266205268</v>
+        <v>37.3146545779375</v>
       </c>
       <c r="I18" t="n">
-        <v>1.761946283766416</v>
+        <v>1.664465845535917</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738296823837388</v>
+        <v>4.738008480879373</v>
       </c>
       <c r="K18" t="n">
-        <v>20.81783244135207</v>
+        <v>19.52859153865811</v>
       </c>
       <c r="L18" t="n">
-        <v>43.65915260222891</v>
+        <v>43.68700825466122</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94131198768457</v>
+        <v>99.94455603180725</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.18503586787556</v>
+        <v>79.60402454716279</v>
       </c>
       <c r="C19" t="n">
-        <v>34.73821485985332</v>
+        <v>36.11807145468999</v>
       </c>
       <c r="D19" t="n">
-        <v>1.229635152230534</v>
+        <v>1.273344230671575</v>
       </c>
       <c r="E19" t="n">
-        <v>11.80451597199151</v>
+        <v>12.29790071401662</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586023683570107</v>
+        <v>0.7585219173798902</v>
       </c>
       <c r="G19" t="n">
-        <v>20.96722071983932</v>
+        <v>21.80929467934162</v>
       </c>
       <c r="H19" t="n">
-        <v>37.21458857557755</v>
+        <v>37.33634006124161</v>
       </c>
       <c r="I19" t="n">
-        <v>1.469208277648324</v>
+        <v>1.387860960887171</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741264802231317</v>
+        <v>4.740761983624313</v>
       </c>
       <c r="K19" t="n">
-        <v>21.81496413212442</v>
+        <v>20.39597545283721</v>
       </c>
       <c r="L19" t="n">
-        <v>43.39787805569541</v>
+        <v>43.4397179300968</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95105704767317</v>
+        <v>99.95376483762399</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.5128462441173</v>
+        <v>77.09969414587663</v>
       </c>
       <c r="C20" t="n">
-        <v>32.29184129388904</v>
+        <v>33.82748960691344</v>
       </c>
       <c r="D20" t="n">
-        <v>1.133610002735001</v>
+        <v>1.183805408998129</v>
       </c>
       <c r="E20" t="n">
-        <v>11.08684013975381</v>
+        <v>11.62599374215103</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590125809610954</v>
+        <v>0.7589013862462146</v>
       </c>
       <c r="G20" t="n">
-        <v>19.32984031437825</v>
+        <v>20.27571208629269</v>
       </c>
       <c r="H20" t="n">
-        <v>37.23471228455382</v>
+        <v>37.35501846500439</v>
       </c>
       <c r="I20" t="n">
-        <v>1.225002290728473</v>
+        <v>1.157129393145339</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743828631006846</v>
+        <v>4.743133664038841</v>
       </c>
       <c r="K20" t="n">
-        <v>24.48715375588269</v>
+        <v>22.90030585412335</v>
       </c>
       <c r="L20" t="n">
-        <v>43.18019360918247</v>
+        <v>43.23365284560523</v>
       </c>
       <c r="M20" t="n">
-        <v>99.9591886589542</v>
+        <v>99.96144830664201</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.55868422631819</v>
+        <v>82.78946205322423</v>
       </c>
       <c r="C21" t="n">
-        <v>36.0181521175391</v>
+        <v>37.38155992507919</v>
       </c>
       <c r="D21" t="n">
-        <v>1.134443387241392</v>
+        <v>1.184579151582454</v>
       </c>
       <c r="E21" t="n">
-        <v>13.10067524279301</v>
+        <v>13.53860143484744</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595705765006572</v>
+        <v>0.7593974089163081</v>
       </c>
       <c r="G21" t="n">
-        <v>21.04994200862242</v>
+        <v>21.92341474999441</v>
       </c>
       <c r="H21" t="n">
-        <v>38.96797692094993</v>
+        <v>39.01388426967127</v>
       </c>
       <c r="I21" t="n">
-        <v>1.798759987081666</v>
+        <v>1.623351232485419</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747316103129108</v>
+        <v>4.746233805726925</v>
       </c>
       <c r="K21" t="n">
-        <v>18.44131577368181</v>
+        <v>17.21053794677575</v>
       </c>
       <c r="L21" t="n">
-        <v>45.48061748936283</v>
+        <v>45.35382576504308</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94008538058374</v>
+        <v>99.94592363689802</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_45_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_45_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.52347777819554</v>
+        <v>45.22183766073933</v>
       </c>
       <c r="M2" t="n">
-        <v>100.587058713254</v>
+        <v>99.10883488949341</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.98444048633721</v>
+        <v>88.00959286252001</v>
       </c>
       <c r="C3" t="n">
-        <v>45.92503928952057</v>
+        <v>45.9096634842259</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228623364505739</v>
+        <v>2.228699589374472</v>
       </c>
       <c r="E3" t="n">
-        <v>5.701855414797826</v>
+        <v>5.694554943100468</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428744548352464</v>
+        <v>0.7428998631248239</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97231992272351</v>
+        <v>33.96669900257291</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17222492242133</v>
+        <v>34.17339370374189</v>
       </c>
       <c r="I3" t="n">
-        <v>6.523577064333261</v>
+        <v>6.560221616075302</v>
       </c>
       <c r="J3" t="n">
-        <v>4.64296534272029</v>
+        <v>4.643124144530149</v>
       </c>
       <c r="K3" t="n">
-        <v>12.01555951366279</v>
+        <v>11.99040713747999</v>
       </c>
       <c r="L3" t="n">
-        <v>48.82522696466126</v>
+        <v>48.86444778544592</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7658257678446</v>
+        <v>106.7645184071518</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.01052204325595</v>
+        <v>87.11209570923759</v>
       </c>
       <c r="C4" t="n">
-        <v>42.57780708382734</v>
+        <v>42.64649813601181</v>
       </c>
       <c r="D4" t="n">
-        <v>2.181367953261001</v>
+        <v>2.185521296543395</v>
       </c>
       <c r="E4" t="n">
-        <v>6.488897364999045</v>
+        <v>6.497281887077047</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444248141512098</v>
+        <v>0.7444571810110323</v>
       </c>
       <c r="G4" t="n">
-        <v>33.25197570734186</v>
+        <v>33.30863629953729</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24354145095564</v>
+        <v>34.24503032650748</v>
       </c>
       <c r="I4" t="n">
-        <v>5.447659664102113</v>
+        <v>5.478311337242397</v>
       </c>
       <c r="J4" t="n">
-        <v>4.65265508844506</v>
+        <v>4.652857381318951</v>
       </c>
       <c r="K4" t="n">
-        <v>12.98947795674407</v>
+        <v>12.88790429076242</v>
       </c>
       <c r="L4" t="n">
-        <v>44.25150448541933</v>
+        <v>44.28336919500146</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81878952599074</v>
+        <v>99.81777162177569</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.73112248793335</v>
+        <v>85.85030913566297</v>
       </c>
       <c r="C5" t="n">
-        <v>42.14388568222246</v>
+        <v>42.23498666521116</v>
       </c>
       <c r="D5" t="n">
-        <v>2.118535526086275</v>
+        <v>2.123613550303066</v>
       </c>
       <c r="E5" t="n">
-        <v>7.059947526121908</v>
+        <v>7.075465561794454</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457411207182818</v>
+        <v>0.745779123519189</v>
       </c>
       <c r="G5" t="n">
-        <v>32.29418115510965</v>
+        <v>32.36512565660534</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30409155304095</v>
+        <v>34.30583968188268</v>
       </c>
       <c r="I5" t="n">
-        <v>4.547743602366999</v>
+        <v>4.573366039563312</v>
       </c>
       <c r="J5" t="n">
-        <v>4.66088200448926</v>
+        <v>4.661119521994929</v>
       </c>
       <c r="K5" t="n">
-        <v>14.26887751206668</v>
+        <v>14.14969086433702</v>
       </c>
       <c r="L5" t="n">
-        <v>43.43591292615246</v>
+        <v>43.46314715552843</v>
       </c>
       <c r="M5" t="n">
-        <v>99.8486761204416</v>
+        <v>99.8478246850766</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.22148973289676</v>
+        <v>84.40273047182944</v>
       </c>
       <c r="C6" t="n">
-        <v>41.34040362888382</v>
+        <v>41.49759495610563</v>
       </c>
       <c r="D6" t="n">
-        <v>2.04448599674306</v>
+        <v>2.052742997900366</v>
       </c>
       <c r="E6" t="n">
-        <v>7.445759870681665</v>
+        <v>7.475485942236457</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468613593426445</v>
+        <v>0.7469033177540987</v>
       </c>
       <c r="G6" t="n">
-        <v>31.16539719769444</v>
+        <v>31.28501655034205</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35562252976164</v>
+        <v>34.35755261668853</v>
       </c>
       <c r="I6" t="n">
-        <v>3.795479282781764</v>
+        <v>3.816883310944845</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667883495891528</v>
+        <v>4.668145735963114</v>
       </c>
       <c r="K6" t="n">
-        <v>15.77851026710328</v>
+        <v>15.59726952817056</v>
       </c>
       <c r="L6" t="n">
-        <v>42.75475989283605</v>
+        <v>42.77809757018036</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87367378882314</v>
+        <v>99.87296205445655</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.53326626780739</v>
+        <v>82.71360969800391</v>
       </c>
       <c r="C7" t="n">
-        <v>40.24143085975881</v>
+        <v>40.40115071648313</v>
       </c>
       <c r="D7" t="n">
-        <v>1.962095249675992</v>
+        <v>1.970312579168244</v>
       </c>
       <c r="E7" t="n">
-        <v>7.673527327885341</v>
+        <v>7.706101693613771</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478166383088558</v>
+        <v>0.7478619473745733</v>
       </c>
       <c r="G7" t="n">
-        <v>29.90946276632614</v>
+        <v>30.02872824882364</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39956536220736</v>
+        <v>34.40164957923037</v>
       </c>
       <c r="I7" t="n">
-        <v>3.166944933973351</v>
+        <v>3.184818478702244</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673853989430349</v>
+        <v>4.674137171091081</v>
       </c>
       <c r="K7" t="n">
-        <v>17.46673373219263</v>
+        <v>17.28639030199607</v>
       </c>
       <c r="L7" t="n">
-        <v>42.18640542797131</v>
+        <v>42.20643444510569</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89457001992274</v>
+        <v>99.89397546358489</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.53541284054218</v>
+        <v>87.57916230397211</v>
       </c>
       <c r="C8" t="n">
-        <v>42.55841072589283</v>
+        <v>42.71693051838646</v>
       </c>
       <c r="D8" t="n">
-        <v>1.966373203822345</v>
+        <v>1.974520921796781</v>
       </c>
       <c r="E8" t="n">
-        <v>9.52197900741435</v>
+        <v>9.54683230901488</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494471021148783</v>
+        <v>0.7494592874853114</v>
       </c>
       <c r="G8" t="n">
-        <v>30.41340146932219</v>
+        <v>30.53735605112841</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47456669728439</v>
+        <v>34.47512722432432</v>
       </c>
       <c r="I8" t="n">
-        <v>5.725600972366045</v>
+        <v>5.611745963439215</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684044388217989</v>
+        <v>4.684120546783194</v>
       </c>
       <c r="K8" t="n">
-        <v>12.4645871594578</v>
+        <v>12.42083769602789</v>
       </c>
       <c r="L8" t="n">
-        <v>44.78656396100385</v>
+        <v>44.67557226831906</v>
       </c>
       <c r="M8" t="n">
-        <v>99.80956184635448</v>
+        <v>99.81334048273341</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.52818443413</v>
+        <v>85.408603523501</v>
       </c>
       <c r="C9" t="n">
-        <v>41.43919473353464</v>
+        <v>41.41701895054305</v>
       </c>
       <c r="D9" t="n">
-        <v>1.875665525556079</v>
+        <v>1.876044203998564</v>
       </c>
       <c r="E9" t="n">
-        <v>9.879439400756118</v>
+        <v>9.85153048476367</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508433375494998</v>
+        <v>0.7508296494475249</v>
       </c>
       <c r="G9" t="n">
-        <v>29.01044854558447</v>
+        <v>29.01434428612056</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53879352727699</v>
+        <v>34.53816387458614</v>
       </c>
       <c r="I9" t="n">
-        <v>4.780223237722486</v>
+        <v>4.685005715537515</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692770859684374</v>
+        <v>4.692685309047029</v>
       </c>
       <c r="K9" t="n">
-        <v>14.47181556586998</v>
+        <v>14.591396476499</v>
       </c>
       <c r="L9" t="n">
-        <v>43.92994522914076</v>
+        <v>43.83570274064019</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84095552854539</v>
+        <v>99.84411816768224</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.40286518936475</v>
+        <v>83.09228256902786</v>
       </c>
       <c r="C10" t="n">
-        <v>40.05499745880901</v>
+        <v>39.82712290812625</v>
       </c>
       <c r="D10" t="n">
-        <v>1.780712411481671</v>
+        <v>1.772160067967602</v>
       </c>
       <c r="E10" t="n">
-        <v>10.04428429508366</v>
+        <v>9.957727453287148</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520406459270725</v>
+        <v>0.7520074427322921</v>
       </c>
       <c r="G10" t="n">
-        <v>27.54183253032665</v>
+        <v>27.40770299150488</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59386971264533</v>
+        <v>34.59234236568543</v>
       </c>
       <c r="I10" t="n">
-        <v>3.989871556856141</v>
+        <v>3.910295730773671</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700254037044203</v>
+        <v>4.700046517076824</v>
       </c>
       <c r="K10" t="n">
-        <v>16.59713481063527</v>
+        <v>16.90771743097217</v>
       </c>
       <c r="L10" t="n">
-        <v>43.2150837517301</v>
+        <v>43.13502061324776</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86721602117437</v>
+        <v>99.86986095234617</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.23513900428389</v>
+        <v>80.58741845376296</v>
       </c>
       <c r="C11" t="n">
-        <v>38.50529252507935</v>
+        <v>37.92783046950116</v>
       </c>
       <c r="D11" t="n">
-        <v>1.684956656651296</v>
+        <v>1.660977923073512</v>
       </c>
       <c r="E11" t="n">
-        <v>10.05907038908509</v>
+        <v>9.876827115848554</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530680628529327</v>
+        <v>0.7530223999924963</v>
       </c>
       <c r="G11" t="n">
-        <v>26.06080227167933</v>
+        <v>25.688192852271</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64113089123489</v>
+        <v>34.63903039965482</v>
       </c>
       <c r="I11" t="n">
-        <v>3.329435339949517</v>
+        <v>3.262977762969464</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706675392830829</v>
+        <v>4.7063899999531</v>
       </c>
       <c r="K11" t="n">
-        <v>18.76486099571611</v>
+        <v>19.41258154623706</v>
       </c>
       <c r="L11" t="n">
-        <v>42.61901671373631</v>
+        <v>42.55096865840698</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88917023453178</v>
+        <v>99.8913806741452</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.01312455631299</v>
+        <v>78.08128454310263</v>
       </c>
       <c r="C12" t="n">
-        <v>36.79830450729073</v>
+        <v>35.92607773649324</v>
       </c>
       <c r="D12" t="n">
-        <v>1.58778022801215</v>
+        <v>1.550957713549882</v>
       </c>
       <c r="E12" t="n">
-        <v>9.941897550479187</v>
+        <v>9.676321777867043</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539505567572816</v>
+        <v>0.7538975388939925</v>
       </c>
       <c r="G12" t="n">
-        <v>24.55779880732561</v>
+        <v>23.98665286150425</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68172561083495</v>
+        <v>34.67928678912364</v>
       </c>
       <c r="I12" t="n">
-        <v>2.777780823170796</v>
+        <v>2.722308244076379</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712190979733009</v>
+        <v>4.711859618087451</v>
       </c>
       <c r="K12" t="n">
-        <v>20.98687544368702</v>
+        <v>21.91871545689737</v>
       </c>
       <c r="L12" t="n">
-        <v>42.12233573402366</v>
+        <v>42.0645685354158</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90751568500141</v>
+        <v>99.9093617288064</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.75873957048459</v>
+        <v>75.57845583608719</v>
       </c>
       <c r="C13" t="n">
-        <v>34.97284504885288</v>
+        <v>33.84309955203256</v>
       </c>
       <c r="D13" t="n">
-        <v>1.490089473158814</v>
+        <v>1.442166414582469</v>
       </c>
       <c r="E13" t="n">
-        <v>9.716397276965665</v>
+        <v>9.376057167038361</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7547092169443205</v>
+        <v>0.7546526030558277</v>
       </c>
       <c r="G13" t="n">
-        <v>23.04684038833362</v>
+        <v>22.30411883760063</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71662397943873</v>
+        <v>34.71401974056806</v>
       </c>
       <c r="I13" t="n">
-        <v>2.31714662974144</v>
+        <v>2.270862304142912</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716932605902001</v>
+        <v>4.716578769098922</v>
       </c>
       <c r="K13" t="n">
-        <v>23.24126042951542</v>
+        <v>24.42154416391282</v>
       </c>
       <c r="L13" t="n">
-        <v>41.70873394321028</v>
+        <v>41.65973661060808</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92283942157857</v>
+        <v>99.92438032655345</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.53225236625738</v>
+        <v>82.784317695254</v>
       </c>
       <c r="C14" t="n">
-        <v>39.23010631197538</v>
+        <v>38.27202819316322</v>
       </c>
       <c r="D14" t="n">
-        <v>1.491817461218846</v>
+        <v>1.443931538450224</v>
       </c>
       <c r="E14" t="n">
-        <v>12.08331923746199</v>
+        <v>11.84104651080137</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555844184266258</v>
+        <v>0.7555762518858434</v>
       </c>
       <c r="G14" t="n">
-        <v>24.94487854041662</v>
+        <v>24.27831652388024</v>
       </c>
       <c r="H14" t="n">
-        <v>36.62819504150589</v>
+        <v>36.70340638982642</v>
       </c>
       <c r="I14" t="n">
-        <v>2.906055052061006</v>
+        <v>3.039688906123401</v>
       </c>
       <c r="J14" t="n">
-        <v>4.72240261516641</v>
+        <v>4.722351574286519</v>
       </c>
       <c r="K14" t="n">
-        <v>16.46774763374261</v>
+        <v>17.215682304746</v>
       </c>
       <c r="L14" t="n">
-        <v>44.20538975636431</v>
+        <v>44.41109040009145</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90324370208231</v>
+        <v>99.89880089800067</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.05089164938815</v>
+        <v>81.93290681622298</v>
       </c>
       <c r="C15" t="n">
-        <v>39.17652104777989</v>
+        <v>37.88963896072602</v>
       </c>
       <c r="D15" t="n">
-        <v>1.472127020463057</v>
+        <v>1.412659151601823</v>
       </c>
       <c r="E15" t="n">
-        <v>12.34920083302163</v>
+        <v>12.00720998075922</v>
       </c>
       <c r="F15" t="n">
-        <v>0.75631954540461</v>
+        <v>0.756355712842493</v>
       </c>
       <c r="G15" t="n">
-        <v>24.63698946602954</v>
+        <v>23.75250149308064</v>
       </c>
       <c r="H15" t="n">
-        <v>36.68518893760541</v>
+        <v>36.74127003652721</v>
       </c>
       <c r="I15" t="n">
-        <v>2.42406868808508</v>
+        <v>2.535687236146023</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726997158778811</v>
+        <v>4.727223205265579</v>
       </c>
       <c r="K15" t="n">
-        <v>16.94910835061187</v>
+        <v>18.06709318377701</v>
       </c>
       <c r="L15" t="n">
-        <v>43.79364685016211</v>
+        <v>43.95883205254911</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91927624855386</v>
+        <v>99.91556419705213</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.7694866993053</v>
+        <v>79.3050529187885</v>
       </c>
       <c r="C16" t="n">
-        <v>37.2699081215145</v>
+        <v>35.65305122364776</v>
       </c>
       <c r="D16" t="n">
-        <v>1.385953672500299</v>
+        <v>1.313960002797141</v>
       </c>
       <c r="E16" t="n">
-        <v>11.96327740797991</v>
+        <v>11.52078651323935</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569505937496251</v>
+        <v>0.7570280766245147</v>
       </c>
       <c r="G16" t="n">
-        <v>23.19482324225955</v>
+        <v>22.09297047550239</v>
       </c>
       <c r="H16" t="n">
-        <v>36.71579786197647</v>
+        <v>36.77393125512923</v>
       </c>
       <c r="I16" t="n">
-        <v>2.02174270990429</v>
+        <v>2.114951116592654</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730941210935156</v>
+        <v>4.731425478903215</v>
       </c>
       <c r="K16" t="n">
-        <v>19.23051330069469</v>
+        <v>20.69494708121149</v>
       </c>
       <c r="L16" t="n">
-        <v>43.43224333645512</v>
+        <v>43.58156593858114</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93266475866432</v>
+        <v>99.92956424344041</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.77059286234862</v>
+        <v>81.07124649115964</v>
       </c>
       <c r="C17" t="n">
-        <v>38.71979700271107</v>
+        <v>36.93052147982517</v>
       </c>
       <c r="D17" t="n">
-        <v>1.387067731520693</v>
+        <v>1.315105464200898</v>
       </c>
       <c r="E17" t="n">
-        <v>12.84919191994658</v>
+        <v>12.33094835730262</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575590467258622</v>
+        <v>0.7576880255129798</v>
       </c>
       <c r="G17" t="n">
-        <v>23.75710210033781</v>
+        <v>22.55897428628801</v>
       </c>
       <c r="H17" t="n">
-        <v>37.2889451668423</v>
+        <v>37.25273338086152</v>
       </c>
       <c r="I17" t="n">
-        <v>1.995982854938743</v>
+        <v>2.120246817537496</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734744042036637</v>
+        <v>4.735550159456122</v>
       </c>
       <c r="K17" t="n">
-        <v>17.22940713765138</v>
+        <v>18.92875350884035</v>
       </c>
       <c r="L17" t="n">
-        <v>43.98431653530017</v>
+        <v>44.07011167549337</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93352067566262</v>
+        <v>99.9293866641589</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.47140846134189</v>
+        <v>78.55661755645595</v>
       </c>
       <c r="C18" t="n">
-        <v>36.72895623848792</v>
+        <v>34.7425659232588</v>
       </c>
       <c r="D18" t="n">
-        <v>1.304027200688455</v>
+        <v>1.224682671316204</v>
       </c>
       <c r="E18" t="n">
-        <v>12.35735154940495</v>
+        <v>11.77780819813873</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580813569406999</v>
+        <v>0.7582565082620141</v>
       </c>
       <c r="G18" t="n">
-        <v>22.334819449955</v>
+        <v>21.0078854077853</v>
       </c>
       <c r="H18" t="n">
-        <v>37.3146545779375</v>
+        <v>37.28068358670918</v>
       </c>
       <c r="I18" t="n">
-        <v>1.664465845535917</v>
+        <v>1.768198007606945</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738008480879373</v>
+        <v>4.739103176637586</v>
       </c>
       <c r="K18" t="n">
-        <v>19.52859153865811</v>
+        <v>21.44338244354405</v>
       </c>
       <c r="L18" t="n">
-        <v>43.68700825466122</v>
+        <v>43.75515588826556</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94455603180725</v>
+        <v>99.94110425506841</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.60402454716279</v>
+        <v>77.5710214012085</v>
       </c>
       <c r="C19" t="n">
-        <v>36.11807145468999</v>
+        <v>34.02861968686687</v>
       </c>
       <c r="D19" t="n">
-        <v>1.273344230671575</v>
+        <v>1.189945704264396</v>
       </c>
       <c r="E19" t="n">
-        <v>12.29790071401662</v>
+        <v>11.68948044875315</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585219173798902</v>
+        <v>0.758736927187477</v>
       </c>
       <c r="G19" t="n">
-        <v>21.80929467934162</v>
+        <v>20.41201658369708</v>
       </c>
       <c r="H19" t="n">
-        <v>37.33634006124161</v>
+        <v>37.30430401825721</v>
       </c>
       <c r="I19" t="n">
-        <v>1.387860960887171</v>
+        <v>1.474431924127455</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740761983624313</v>
+        <v>4.74210579492173</v>
       </c>
       <c r="K19" t="n">
-        <v>20.39597545283721</v>
+        <v>22.4289785987915</v>
       </c>
       <c r="L19" t="n">
-        <v>43.4397179300968</v>
+        <v>43.49328510301922</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95376483762399</v>
+        <v>99.9508833886776</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.09969414587663</v>
+        <v>74.96563970872425</v>
       </c>
       <c r="C20" t="n">
-        <v>33.82748960691344</v>
+        <v>31.64958018310221</v>
       </c>
       <c r="D20" t="n">
-        <v>1.183805408998129</v>
+        <v>1.097420350387819</v>
       </c>
       <c r="E20" t="n">
-        <v>11.62599374215103</v>
+        <v>10.98544799145103</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589013862462146</v>
+        <v>0.7591516792271584</v>
       </c>
       <c r="G20" t="n">
-        <v>20.27571208629269</v>
+        <v>18.82486092527262</v>
       </c>
       <c r="H20" t="n">
-        <v>37.35501846500439</v>
+        <v>37.32469585055911</v>
       </c>
       <c r="I20" t="n">
-        <v>1.157129393145339</v>
+        <v>1.229364916656762</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743133664038841</v>
+        <v>4.744697995169739</v>
       </c>
       <c r="K20" t="n">
-        <v>22.90030585412335</v>
+        <v>25.03436029127577</v>
       </c>
       <c r="L20" t="n">
-        <v>43.23365284560523</v>
+        <v>43.27510308328515</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96144830664201</v>
+        <v>99.95904355766312</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.78946205322423</v>
+        <v>81.19298320648625</v>
       </c>
       <c r="C21" t="n">
-        <v>37.38155992507919</v>
+        <v>35.49176956867504</v>
       </c>
       <c r="D21" t="n">
-        <v>1.184579151582454</v>
+        <v>1.098236374881237</v>
       </c>
       <c r="E21" t="n">
-        <v>13.53860143484744</v>
+        <v>13.05841753203154</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7593974089163081</v>
+        <v>0.7597161724628172</v>
       </c>
       <c r="G21" t="n">
-        <v>21.92341474999441</v>
+        <v>20.60179061032479</v>
       </c>
       <c r="H21" t="n">
-        <v>39.01388426967127</v>
+        <v>39.11538172157765</v>
       </c>
       <c r="I21" t="n">
-        <v>1.623351232485419</v>
+        <v>1.811214717315612</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746233805726925</v>
+        <v>4.748226077892606</v>
       </c>
       <c r="K21" t="n">
-        <v>17.21053794677575</v>
+        <v>18.80701679351375</v>
       </c>
       <c r="L21" t="n">
-        <v>45.35382576504308</v>
+        <v>45.64088467356863</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94592363689802</v>
+        <v>99.93967103575741</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_45_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_45_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.22183766073933</v>
+        <v>43.41406565700372</v>
       </c>
       <c r="M2" t="n">
-        <v>99.10883488949341</v>
+        <v>96.4564102563285</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.00959286252001</v>
+        <v>81.45344637612547</v>
       </c>
       <c r="C3" t="n">
-        <v>45.9096634842259</v>
+        <v>43.20900193168103</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228699589374472</v>
+        <v>2.179185126636568</v>
       </c>
       <c r="E3" t="n">
-        <v>5.694554943100468</v>
+        <v>4.144208836283258</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428998631248239</v>
+        <v>0.7376164203201268</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96669900257291</v>
+        <v>32.77857627982505</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17339370374189</v>
+        <v>33.93035533472582</v>
       </c>
       <c r="I3" t="n">
-        <v>6.560221616075302</v>
+        <v>3.073401751333861</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643124144530149</v>
+        <v>4.610102627000792</v>
       </c>
       <c r="K3" t="n">
-        <v>11.99040713747999</v>
+        <v>18.54655362387452</v>
       </c>
       <c r="L3" t="n">
-        <v>48.86444778544592</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7645184071518</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.11209570923759</v>
+        <v>88.4086056397076</v>
       </c>
       <c r="C4" t="n">
-        <v>42.64649813601181</v>
+        <v>42.75631854148702</v>
       </c>
       <c r="D4" t="n">
-        <v>2.185521296543395</v>
+        <v>2.184854664138215</v>
       </c>
       <c r="E4" t="n">
-        <v>6.497281887077047</v>
+        <v>6.487888755577929</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444571810110323</v>
+        <v>0.7395354605639863</v>
       </c>
       <c r="G4" t="n">
-        <v>33.30863629953729</v>
+        <v>33.45527782470219</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24503032650748</v>
+        <v>34.01863118594336</v>
       </c>
       <c r="I4" t="n">
-        <v>5.478311337242397</v>
+        <v>6.900321120256996</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652857381318951</v>
+        <v>4.622096628524915</v>
       </c>
       <c r="K4" t="n">
-        <v>12.88790429076242</v>
+        <v>11.5913943602924</v>
       </c>
       <c r="L4" t="n">
-        <v>44.28336919500146</v>
+        <v>45.42287325510787</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81777162177569</v>
+        <v>99.77058615688729</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.85030913566297</v>
+        <v>87.12680452029784</v>
       </c>
       <c r="C5" t="n">
-        <v>42.23498666521116</v>
+        <v>42.54413351894155</v>
       </c>
       <c r="D5" t="n">
-        <v>2.123613550303066</v>
+        <v>2.12304817645333</v>
       </c>
       <c r="E5" t="n">
-        <v>7.075465561794454</v>
+        <v>7.264846418092532</v>
       </c>
       <c r="F5" t="n">
-        <v>0.745779123519189</v>
+        <v>0.7411659969766939</v>
       </c>
       <c r="G5" t="n">
-        <v>32.36512565660534</v>
+        <v>32.50887472942701</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30583968188268</v>
+        <v>34.09363586092791</v>
       </c>
       <c r="I5" t="n">
-        <v>4.573366039563312</v>
+        <v>5.76294585731601</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661119521994929</v>
+        <v>4.632287481104338</v>
       </c>
       <c r="K5" t="n">
-        <v>14.14969086433702</v>
+        <v>12.8731954797022</v>
       </c>
       <c r="L5" t="n">
-        <v>43.46314715552843</v>
+        <v>44.39099541468244</v>
       </c>
       <c r="M5" t="n">
-        <v>99.8478246850766</v>
+        <v>99.80832441332618</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.40273047182944</v>
+        <v>85.58722151225997</v>
       </c>
       <c r="C6" t="n">
-        <v>41.49759495610563</v>
+        <v>41.89876145976116</v>
       </c>
       <c r="D6" t="n">
-        <v>2.052742997900366</v>
+        <v>2.048864586314922</v>
       </c>
       <c r="E6" t="n">
-        <v>7.475485942236457</v>
+        <v>7.812907047814353</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469033177540987</v>
+        <v>0.7425548671777004</v>
       </c>
       <c r="G6" t="n">
-        <v>31.28501655034205</v>
+        <v>31.372949004549</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35755261668853</v>
+        <v>34.15752389017421</v>
       </c>
       <c r="I6" t="n">
-        <v>3.816883310944845</v>
+        <v>4.811454196369152</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668145735963114</v>
+        <v>4.640967919860628</v>
       </c>
       <c r="K6" t="n">
-        <v>15.59726952817056</v>
+        <v>14.41277848774005</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77809757018036</v>
+        <v>43.52837822312892</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87296205445655</v>
+        <v>99.83991817063011</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.71360969800391</v>
+        <v>83.89256492459815</v>
       </c>
       <c r="C7" t="n">
-        <v>40.40115071648313</v>
+        <v>40.95087644546764</v>
       </c>
       <c r="D7" t="n">
-        <v>1.970312579168244</v>
+        <v>1.967795693455332</v>
       </c>
       <c r="E7" t="n">
-        <v>7.706101693613771</v>
+        <v>8.173092002739867</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478619473745733</v>
+        <v>0.743739738994081</v>
       </c>
       <c r="G7" t="n">
-        <v>30.02872824882364</v>
+        <v>30.13159305622171</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40164957923037</v>
+        <v>34.21202799372772</v>
       </c>
       <c r="I7" t="n">
-        <v>3.184818478702244</v>
+        <v>4.015943070746411</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674137171091081</v>
+        <v>4.648373368713007</v>
       </c>
       <c r="K7" t="n">
-        <v>17.28639030199607</v>
+        <v>16.10743507540188</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20643444510569</v>
+        <v>42.8080369736758</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89397546358489</v>
+        <v>99.86634849454531</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.57916230397211</v>
+        <v>81.94511628663007</v>
       </c>
       <c r="C8" t="n">
-        <v>42.71693051838646</v>
+        <v>39.62654172437995</v>
       </c>
       <c r="D8" t="n">
-        <v>1.974520921796781</v>
+        <v>1.8751921208186</v>
       </c>
       <c r="E8" t="n">
-        <v>9.54683230901488</v>
+        <v>8.347000213184689</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494592874853114</v>
+        <v>0.7447535910286425</v>
       </c>
       <c r="G8" t="n">
-        <v>30.53735605112841</v>
+        <v>28.71361395629662</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47512722432432</v>
+        <v>34.25866518731755</v>
       </c>
       <c r="I8" t="n">
-        <v>5.611745963439215</v>
+        <v>3.351181274054958</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684120546783194</v>
+        <v>4.654709943929016</v>
       </c>
       <c r="K8" t="n">
-        <v>12.42083769602789</v>
+        <v>18.05488371336993</v>
       </c>
       <c r="L8" t="n">
-        <v>44.67557226831906</v>
+        <v>42.20702058806274</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81334048273341</v>
+        <v>99.88844602581261</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.408603523501</v>
+        <v>79.96604085879473</v>
       </c>
       <c r="C9" t="n">
-        <v>41.41701895054305</v>
+        <v>38.16692629711193</v>
       </c>
       <c r="D9" t="n">
-        <v>1.876044203998564</v>
+        <v>1.781951995595194</v>
       </c>
       <c r="E9" t="n">
-        <v>9.85153048476367</v>
+        <v>8.397946851079455</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508296494475249</v>
+        <v>0.745621568168947</v>
       </c>
       <c r="G9" t="n">
-        <v>29.01434428612056</v>
+        <v>27.28588773497861</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53816387458614</v>
+        <v>34.29859213577156</v>
       </c>
       <c r="I9" t="n">
-        <v>4.685005715537515</v>
+        <v>2.795905772145033</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692685309047029</v>
+        <v>4.66013480105592</v>
       </c>
       <c r="K9" t="n">
-        <v>14.591396476499</v>
+        <v>20.03395914120529</v>
       </c>
       <c r="L9" t="n">
-        <v>43.83570274064019</v>
+        <v>41.70602619295903</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84411816768224</v>
+        <v>99.90691163127624</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.09228256902786</v>
+        <v>85.2317950869872</v>
       </c>
       <c r="C10" t="n">
-        <v>39.82712290812625</v>
+        <v>41.75570193499935</v>
       </c>
       <c r="D10" t="n">
-        <v>1.772160067967602</v>
+        <v>1.783968121460161</v>
       </c>
       <c r="E10" t="n">
-        <v>9.957727453287148</v>
+        <v>10.42268149947708</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520074427322921</v>
+        <v>0.7464651750297259</v>
       </c>
       <c r="G10" t="n">
-        <v>27.40770299150488</v>
+        <v>28.84983013485332</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59234236568543</v>
+        <v>35.87046880927471</v>
       </c>
       <c r="I10" t="n">
-        <v>3.910295730773671</v>
+        <v>2.892974002956425</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700046517076824</v>
+        <v>4.665407343935787</v>
       </c>
       <c r="K10" t="n">
-        <v>16.90771743097217</v>
+        <v>14.76820491301279</v>
       </c>
       <c r="L10" t="n">
-        <v>43.13502061324776</v>
+        <v>43.37976966698534</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86986095234617</v>
+        <v>99.90367651499749</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.58741845376296</v>
+        <v>84.80386108018305</v>
       </c>
       <c r="C11" t="n">
-        <v>37.92783046950116</v>
+        <v>41.66584647127558</v>
       </c>
       <c r="D11" t="n">
-        <v>1.660977923073512</v>
+        <v>1.757983731537911</v>
       </c>
       <c r="E11" t="n">
-        <v>9.876827115848554</v>
+        <v>10.72777093367521</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530223999924963</v>
+        <v>0.7471922995425521</v>
       </c>
       <c r="G11" t="n">
-        <v>25.688192852271</v>
+        <v>28.47348580489037</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63903039965482</v>
+        <v>35.94927779351214</v>
       </c>
       <c r="I11" t="n">
-        <v>3.262977762969464</v>
+        <v>2.478198644883921</v>
       </c>
       <c r="J11" t="n">
-        <v>4.7063899999531</v>
+        <v>4.669951872140952</v>
       </c>
       <c r="K11" t="n">
-        <v>19.41258154623706</v>
+        <v>15.19613891981693</v>
       </c>
       <c r="L11" t="n">
-        <v>42.55096865840698</v>
+        <v>43.05548837541784</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8913806741452</v>
+        <v>99.91747376651035</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.08128454310263</v>
+        <v>82.72801446441545</v>
       </c>
       <c r="C12" t="n">
-        <v>35.92607773649324</v>
+        <v>39.9747804101123</v>
       </c>
       <c r="D12" t="n">
-        <v>1.550957713549882</v>
+        <v>1.670277584873932</v>
       </c>
       <c r="E12" t="n">
-        <v>9.676321777867043</v>
+        <v>10.53704127981303</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538975388939925</v>
+        <v>0.7478145639092046</v>
       </c>
       <c r="G12" t="n">
-        <v>23.98665286150425</v>
+        <v>27.0529381187899</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67928678912364</v>
+        <v>35.97921647809373</v>
       </c>
       <c r="I12" t="n">
-        <v>2.722308244076379</v>
+        <v>2.066885414503114</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711859618087451</v>
+        <v>4.67384102443253</v>
       </c>
       <c r="K12" t="n">
-        <v>21.91871545689737</v>
+        <v>17.27198553558456</v>
       </c>
       <c r="L12" t="n">
-        <v>42.0645685354158</v>
+        <v>42.68439520305635</v>
       </c>
       <c r="M12" t="n">
-        <v>99.9093617288064</v>
+        <v>99.93116114875322</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.57845583608719</v>
+        <v>83.91607644870972</v>
       </c>
       <c r="C13" t="n">
-        <v>33.84309955203256</v>
+        <v>40.96143695213919</v>
       </c>
       <c r="D13" t="n">
-        <v>1.442166414582469</v>
+        <v>1.671553051317971</v>
       </c>
       <c r="E13" t="n">
-        <v>9.376057167038361</v>
+        <v>11.18233546747689</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546526030558277</v>
+        <v>0.7483856141294003</v>
       </c>
       <c r="G13" t="n">
-        <v>22.30411883760063</v>
+        <v>27.39044201424527</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71401974056806</v>
+        <v>36.32353670672663</v>
       </c>
       <c r="I13" t="n">
-        <v>2.270862304142912</v>
+        <v>1.922413506504789</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716578769098922</v>
+        <v>4.677410088308753</v>
       </c>
       <c r="K13" t="n">
-        <v>24.42154416391282</v>
+        <v>16.08392355129028</v>
       </c>
       <c r="L13" t="n">
-        <v>41.65973661060808</v>
+        <v>42.89060794247692</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92438032655345</v>
+        <v>99.9359684459064</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.784317695254</v>
+        <v>81.71258299643593</v>
       </c>
       <c r="C14" t="n">
-        <v>38.27202819316322</v>
+        <v>39.05622457079918</v>
       </c>
       <c r="D14" t="n">
-        <v>1.443931538450224</v>
+        <v>1.581063937459519</v>
       </c>
       <c r="E14" t="n">
-        <v>11.84104651080137</v>
+        <v>10.84415896326608</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555762518858434</v>
+        <v>0.7488750149694712</v>
       </c>
       <c r="G14" t="n">
-        <v>24.27831652388024</v>
+        <v>25.90766716357204</v>
       </c>
       <c r="H14" t="n">
-        <v>36.70340638982642</v>
+        <v>36.34729019562727</v>
       </c>
       <c r="I14" t="n">
-        <v>3.039688906123401</v>
+        <v>1.603058877982347</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722351574286519</v>
+        <v>4.680468843559196</v>
       </c>
       <c r="K14" t="n">
-        <v>17.215682304746</v>
+        <v>18.28741700356408</v>
       </c>
       <c r="L14" t="n">
-        <v>44.41109040009145</v>
+        <v>42.60295805045604</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89880089800067</v>
+        <v>99.9465996248193</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.93290681622298</v>
+        <v>80.68389793444908</v>
       </c>
       <c r="C15" t="n">
-        <v>37.88963896072602</v>
+        <v>38.24200432273351</v>
       </c>
       <c r="D15" t="n">
-        <v>1.412659151601823</v>
+        <v>1.537889418827294</v>
       </c>
       <c r="E15" t="n">
-        <v>12.00720998075922</v>
+        <v>10.77624998213543</v>
       </c>
       <c r="F15" t="n">
-        <v>0.756355712842493</v>
+        <v>0.7492986551338823</v>
       </c>
       <c r="G15" t="n">
-        <v>23.75250149308064</v>
+        <v>25.20019984857628</v>
       </c>
       <c r="H15" t="n">
-        <v>36.74127003652721</v>
+        <v>36.36785193381665</v>
       </c>
       <c r="I15" t="n">
-        <v>2.535687236146023</v>
+        <v>1.369291501372774</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727223205265579</v>
+        <v>4.683116594586766</v>
       </c>
       <c r="K15" t="n">
-        <v>18.06709318377701</v>
+        <v>19.31610206555093</v>
       </c>
       <c r="L15" t="n">
-        <v>43.95883205254911</v>
+        <v>42.39627636744042</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91556419705213</v>
+        <v>99.95438275572485</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.3050529187885</v>
+        <v>78.1432232331517</v>
       </c>
       <c r="C16" t="n">
-        <v>35.65305122364776</v>
+        <v>35.91314257856619</v>
       </c>
       <c r="D16" t="n">
-        <v>1.313960002797141</v>
+        <v>1.434433403160278</v>
       </c>
       <c r="E16" t="n">
-        <v>11.52078651323935</v>
+        <v>10.2415882581254</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570280766245147</v>
+        <v>0.7496635506162045</v>
       </c>
       <c r="G16" t="n">
-        <v>22.09297047550239</v>
+        <v>23.50494644580935</v>
       </c>
       <c r="H16" t="n">
-        <v>36.77393125512923</v>
+        <v>36.38556244855132</v>
       </c>
       <c r="I16" t="n">
-        <v>2.114951116592654</v>
+        <v>1.141631935537878</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731425478903215</v>
+        <v>4.68539719135128</v>
       </c>
       <c r="K16" t="n">
-        <v>20.69494708121149</v>
+        <v>21.85677676684829</v>
       </c>
       <c r="L16" t="n">
-        <v>43.58156593858114</v>
+        <v>42.19204477954739</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92956424344041</v>
+        <v>99.96196412496187</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.07124649115964</v>
+        <v>83.23671685484797</v>
       </c>
       <c r="C17" t="n">
-        <v>36.93052147982517</v>
+        <v>39.28874150536047</v>
       </c>
       <c r="D17" t="n">
-        <v>1.315105464200898</v>
+        <v>1.435158143708108</v>
       </c>
       <c r="E17" t="n">
-        <v>12.33094835730262</v>
+        <v>12.03180340211154</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576880255129798</v>
+        <v>0.7500423145038582</v>
       </c>
       <c r="G17" t="n">
-        <v>22.55897428628801</v>
+        <v>25.0915880918959</v>
       </c>
       <c r="H17" t="n">
-        <v>37.25273338086152</v>
+        <v>37.97871196365266</v>
       </c>
       <c r="I17" t="n">
-        <v>2.120246817537496</v>
+        <v>1.261648473326808</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735550159456122</v>
+        <v>4.687764465649115</v>
       </c>
       <c r="K17" t="n">
-        <v>18.92875350884035</v>
+        <v>16.76328314515203</v>
       </c>
       <c r="L17" t="n">
-        <v>44.07011167549337</v>
+        <v>43.90594163770643</v>
       </c>
       <c r="M17" t="n">
-        <v>99.9293866641589</v>
+        <v>99.95796628821893</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.55661755645595</v>
+        <v>84.83404000461162</v>
       </c>
       <c r="C18" t="n">
-        <v>34.7425659232588</v>
+        <v>40.02554724474381</v>
       </c>
       <c r="D18" t="n">
-        <v>1.224682671316204</v>
+        <v>1.436328032474092</v>
       </c>
       <c r="E18" t="n">
-        <v>11.77780819813873</v>
+        <v>12.63522715429138</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7582565082620141</v>
+        <v>0.7506537217425642</v>
       </c>
       <c r="G18" t="n">
-        <v>21.0078854077853</v>
+        <v>25.23596570784586</v>
       </c>
       <c r="H18" t="n">
-        <v>37.28068358670918</v>
+        <v>38.00967082952234</v>
       </c>
       <c r="I18" t="n">
-        <v>1.768198007606945</v>
+        <v>2.074608797844363</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739103176637586</v>
+        <v>4.691585760891027</v>
       </c>
       <c r="K18" t="n">
-        <v>21.44338244354405</v>
+        <v>15.16595999538839</v>
       </c>
       <c r="L18" t="n">
-        <v>43.75515588826556</v>
+        <v>44.73939545888183</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94110425506841</v>
+        <v>99.93090269901403</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.5710214012085</v>
+        <v>81.87558256777203</v>
       </c>
       <c r="C19" t="n">
-        <v>34.02861968686687</v>
+        <v>37.38785729032601</v>
       </c>
       <c r="D19" t="n">
-        <v>1.189945704264396</v>
+        <v>1.329159175007775</v>
       </c>
       <c r="E19" t="n">
-        <v>11.68948044875315</v>
+        <v>11.98081700866351</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758736927187477</v>
+        <v>0.75118244052505</v>
       </c>
       <c r="G19" t="n">
-        <v>20.41201658369708</v>
+        <v>23.35303259589479</v>
       </c>
       <c r="H19" t="n">
-        <v>37.30430401825721</v>
+        <v>38.03644273020247</v>
       </c>
       <c r="I19" t="n">
-        <v>1.474431924127455</v>
+        <v>1.730058364196858</v>
       </c>
       <c r="J19" t="n">
-        <v>4.74210579492173</v>
+        <v>4.694890253281564</v>
       </c>
       <c r="K19" t="n">
-        <v>22.4289785987915</v>
+        <v>18.12441743222798</v>
       </c>
       <c r="L19" t="n">
-        <v>43.49328510301922</v>
+        <v>44.43009725528367</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9508833886776</v>
+        <v>99.94237197783767</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.96563970872425</v>
+        <v>78.8886642649863</v>
       </c>
       <c r="C20" t="n">
-        <v>31.64958018310221</v>
+        <v>34.66755880122165</v>
       </c>
       <c r="D20" t="n">
-        <v>1.097420350387819</v>
+        <v>1.221617375613615</v>
       </c>
       <c r="E20" t="n">
-        <v>10.98544799145103</v>
+        <v>11.25188568591282</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7591516792271584</v>
+        <v>0.7516403226834205</v>
       </c>
       <c r="G20" t="n">
-        <v>18.82486092527262</v>
+        <v>21.46354697679405</v>
       </c>
       <c r="H20" t="n">
-        <v>37.32469585055911</v>
+        <v>38.05962778825823</v>
       </c>
       <c r="I20" t="n">
-        <v>1.229364916656762</v>
+        <v>1.442594098952797</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744697995169739</v>
+        <v>4.697752016771379</v>
       </c>
       <c r="K20" t="n">
-        <v>25.03436029127577</v>
+        <v>21.11133573501369</v>
       </c>
       <c r="L20" t="n">
-        <v>43.27510308328515</v>
+        <v>44.17304828698142</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95904355766312</v>
+        <v>99.95194282321677</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.19298320648625</v>
+        <v>75.93336805575437</v>
       </c>
       <c r="C21" t="n">
-        <v>35.49176956867504</v>
+        <v>31.93375444329321</v>
       </c>
       <c r="D21" t="n">
-        <v>1.098236374881237</v>
+        <v>1.115825701541493</v>
       </c>
       <c r="E21" t="n">
-        <v>13.05841753203154</v>
+        <v>10.47794206651314</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7597161724628172</v>
+        <v>0.7520371927157273</v>
       </c>
       <c r="G21" t="n">
-        <v>20.60179061032479</v>
+        <v>19.60481067234346</v>
       </c>
       <c r="H21" t="n">
-        <v>39.11538172157765</v>
+        <v>38.07972347133173</v>
       </c>
       <c r="I21" t="n">
-        <v>1.811214717315612</v>
+        <v>1.202796496835531</v>
       </c>
       <c r="J21" t="n">
-        <v>4.748226077892606</v>
+        <v>4.700232454473297</v>
       </c>
       <c r="K21" t="n">
-        <v>18.80701679351375</v>
+        <v>24.06663194424561</v>
       </c>
       <c r="L21" t="n">
-        <v>45.64088467356863</v>
+        <v>43.95954155415694</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93967103575741</v>
+        <v>99.95992794169577</v>
       </c>
     </row>
   </sheetData>
